--- a/test/groups.xlsx
+++ b/test/groups.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Информация о группе" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Дисциплины" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Студенты" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Информация о группе" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Дисциплины" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Студенты" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -60,19 +60,19 @@
     <t xml:space="preserve">Математика</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-01</t>
+    <t xml:space="preserve">2026-01-12</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Русский язык</t>
-  </si>
-  <si>
     <t xml:space="preserve">Информатика</t>
   </si>
   <si>
-    <t xml:space="preserve">Литература</t>
+    <t xml:space="preserve">Английский язык</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электротехника</t>
   </si>
   <si>
     <t xml:space="preserve">full_name</t>
@@ -81,10 +81,10 @@
     <t xml:space="preserve">email</t>
   </si>
   <si>
-    <t xml:space="preserve">Иванов Иван Иванович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ivanov123@example.com</t>
+    <t xml:space="preserve">Студент СА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stud503@sa.ru</t>
   </si>
 </sst>
 </file>
@@ -97,7 +97,7 @@
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -160,12 +160,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,210 +177,38 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546a"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ed7d31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="ffc000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472c4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70ad47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563c1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954f72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>5</v>
       </c>
     </row>
@@ -404,106 +228,98 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="0" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="0" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -521,28 +337,31 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="stud503@sa.ru"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
